--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,6 +495,11 @@
           <t>Purpose</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -546,6 +552,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -598,6 +609,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -650,6 +666,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -702,6 +723,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,6 +780,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -806,6 +837,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -858,6 +894,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -910,6 +951,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -962,6 +1008,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1014,6 +1065,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1066,6 +1122,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1118,6 +1179,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1170,6 +1236,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1222,6 +1293,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1274,6 +1350,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1326,6 +1407,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1374,6 +1460,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1426,6 +1517,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1478,6 +1574,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1530,6 +1631,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1582,6 +1688,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1634,6 +1745,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1686,6 +1802,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1738,6 +1859,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1790,6 +1916,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1842,6 +1973,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1894,6 +2030,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1946,6 +2087,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1998,6 +2144,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2050,6 +2201,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2102,6 +2258,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2154,6 +2315,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2206,6 +2372,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2258,6 +2429,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2310,6 +2486,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2362,6 +2543,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2414,6 +2600,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2466,6 +2657,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2514,6 +2710,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2566,6 +2767,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2618,6 +2824,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2670,6 +2881,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2722,6 +2938,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2774,6 +2995,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2824,6 +3050,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2874,6 +3105,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2924,6 +3160,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2974,6 +3215,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3024,6 +3270,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3074,6 +3325,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3126,6 +3382,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-PAY-01</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3178,6 +3439,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-PAY-01</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3230,6 +3496,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3282,6 +3553,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3334,6 +3610,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3386,6 +3667,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3438,6 +3724,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3486,6 +3777,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3534,6 +3830,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3582,6 +3883,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3630,6 +3936,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3678,6 +3989,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3730,6 +4046,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3782,6 +4103,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3834,6 +4160,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3886,6 +4217,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3938,6 +4274,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3990,6 +4331,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4042,6 +4388,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4094,6 +4445,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4146,6 +4502,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4198,6 +4559,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4250,6 +4616,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4302,6 +4673,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4354,6 +4730,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4406,6 +4787,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4458,6 +4844,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4506,6 +4897,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4554,6 +4950,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4602,6 +5003,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4650,6 +5056,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4698,6 +5109,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4750,6 +5166,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4802,6 +5223,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4854,6 +5280,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4906,6 +5337,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4958,6 +5394,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5006,6 +5447,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5054,6 +5500,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5102,6 +5553,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5150,6 +5606,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5198,6 +5659,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5250,6 +5716,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5302,6 +5773,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5354,6 +5830,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5406,6 +5887,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5458,6 +5944,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5510,6 +6001,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5562,6 +6058,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5614,6 +6115,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5666,6 +6172,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5718,6 +6229,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5770,6 +6286,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5822,6 +6343,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5874,6 +6400,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5926,6 +6457,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5978,6 +6514,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6026,6 +6567,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6074,6 +6620,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6122,6 +6673,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6170,6 +6726,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6216,6 +6777,912 @@
       <c r="J113" s="2" t="inlineStr">
         <is>
           <t>NEG-01</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Synthetic-FirstName</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Synthetic-LastName</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>enh02.reg02.1789489772174@example.test</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Synthetic-Pw-One-1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>confirm_password</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Synthetic-Pw-Two-2</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Synthetic-FirstName</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Synthetic-LastName</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>not-an-email</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Synthetic-Pw-1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>confirm_password</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Synthetic-Pw-1</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>REQ-REG-05, REQ-REG-04, REQ-AUTH-01, REQ-AUTH-02, REQ-AUTH-03, REQ-ACCT-01, REQ-CART-05, REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Enh02Shared</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>REQ-REG-05, REQ-REG-04, REQ-AUTH-01, REQ-AUTH-02, REQ-AUTH-03, REQ-ACCT-01, REQ-CART-05, REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SyntheticUser</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>REQ-REG-05, REQ-REG-04, REQ-AUTH-01, REQ-AUTH-02, REQ-AUTH-03, REQ-ACCT-01, REQ-CART-05, REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>enh02.shared.1789489772174@example.test</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>REQ-REG-05, REQ-REG-04, REQ-AUTH-01, REQ-AUTH-02, REQ-AUTH-03, REQ-ACCT-01, REQ-CART-05, REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Enh02-Synthetic-Pw1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>REQ-REG-05, REQ-REG-04, REQ-AUTH-01, REQ-AUTH-02, REQ-AUTH-03, REQ-ACCT-01, REQ-CART-05, REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>confirm_password</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Enh02-Synthetic-Pw1</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-01-01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-01-VALID-KEYWORD</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>search_term</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>A real, known keyword expected to match existing products.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-02-01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-02-NO-RESULTS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-02</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>search_term</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>zzzznoresultxyz123</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>A nonsense keyword guaranteed to match nothing.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>
       </c>
     </row>
@@ -6230,7 +7697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6238,6 +7705,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6266,6 +7734,11 @@
           <t>Purpose</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6293,6 +7766,11 @@
           <t>mechanism check -- no real field needed</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6320,6 +7798,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6347,6 +7830,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6374,6 +7862,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-ACO-03</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6401,6 +7894,11 @@
           <t>REQ-ACO-03 acceptance criteria ("required fields left blank... progression blocked")</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6428,6 +7926,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6455,6 +7958,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6482,6 +7990,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6509,6 +8022,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6536,6 +8054,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-CART-03</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6563,6 +8086,11 @@
           <t>REQ-CART-03/NEG-07</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6590,6 +8118,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-PAY-01</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6617,6 +8150,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-PAY-01</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6644,6 +8182,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6671,6 +8214,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6698,6 +8246,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6725,6 +8278,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6752,6 +8310,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6779,6 +8342,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6806,6 +8374,11 @@
           <t>Valid data satisfying all mandatory fields for REQ-REG-01</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6833,6 +8406,11 @@
           <t>NEG-01</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6860,6 +8438,11 @@
           <t>NEG-02/REQ-REG-02</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6887,6 +8470,11 @@
           <t>NEG-03/REQ-REG-03</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6914,6 +8502,11 @@
           <t>NEG-04/REQ-REG-04/Business Rule #1</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6939,6 +8532,171 @@
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>NEG-01</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, mismatched passwords</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Valid identity fields, malformed email</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>The one, real, shared account this enhancement creates -- reused read-only by every dependent testcase.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-01-VALID-KEYWORD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-01-01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>A real, known keyword expected to match existing products.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-02-NO-RESULTS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-02-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>A nonsense keyword guaranteed to match nothing.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>
       </c>
     </row>

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789489772174@example.test</t>
+          <t>enh02.reg02.1789496029471@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789489772174@example.test</t>
+          <t>enh02.shared.1789496029471@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7681,6 +7681,483 @@
         </is>
       </c>
       <c r="K130" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Enh02Checkout</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SyntheticCustomer</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>enh02.checkout.contact@example.test</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>country_id</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>state_label</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>address1</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1 Enhancement02 Test Way</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>zip_postal_code</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>5555550100</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>
@@ -7697,7 +8174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8700,6 +9177,38 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789496029471@example.test</t>
+          <t>enh02.reg02.1789496368759@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789496029471@example.test</t>
+          <t>enh02.shared.1789496368759@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789496368759@example.test</t>
+          <t>enh02.reg02.1789497486439@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789496368759@example.test</t>
+          <t>enh02.shared.1789497486439@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7689,17 +7689,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Enh02Checkout</t>
+          <t>Enh02GuestCheckout</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7742,17 +7742,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7783,7 +7783,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7795,17 +7795,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>enh02.checkout.contact@example.test</t>
+          <t>enh02.gco03.guest.contact@example.test</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7836,7 +7836,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -7848,17 +7848,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7889,7 +7889,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -7901,17 +7901,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7942,7 +7942,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -7954,17 +7954,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7995,7 +7995,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8007,17 +8007,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1 Enhancement02 Test Way</t>
+          <t>1 Enhancement02 GCO03 Test Way</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8048,7 +8048,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8060,17 +8060,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8101,7 +8101,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENH02-TD-ACO-01-01</t>
+          <t>ENH02-TD-GCO-03-01</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+          <t>REQ-GCO-03</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5555550100</t>
+          <t>5555550200</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8154,10 +8154,487 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr">
         <is>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Enh02Checkout</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
           <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SyntheticCustomer</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>enh02.checkout.contact@example.test</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>country_id</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>state_label</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>address1</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1 Enhancement02 Test Way</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>zip_postal_code</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02, REQ-OHIST-01, REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>5555550100</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>
@@ -8174,7 +8651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9180,30 +9657,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENH02-TD-GCO-03-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic Billing/Shipping contact used by the ONE real, guest-path, order-completing checkout authorized by the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization). Deliberately independent of ENH02-TD-ACO-01-01 (the authenticated-path dataset) -- this checkout must remain genuinely anonymous; no account credentials are used or created.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>ENH02-TD-ACO-01-01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Synthetic Billing/Shipping address contact used by the ONE real, order-completing checkout this enhancement performs -- reused (read-only afterward) by REQ-OHIST-01/REQ-ACO-02.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789497486439@example.test</t>
+          <t>enh02.reg02.1789502050395@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789497486439@example.test</t>
+          <t>enh02.shared.1789502050395@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789502050395@example.test</t>
+          <t>enh02.reg02.1789504941917@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789502050395@example.test</t>
+          <t>enh02.shared.1789504941917@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789504941917@example.test</t>
+          <t>enh02.reg02.1789505041145@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789504941917@example.test</t>
+          <t>enh02.shared.1789505041145@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">

--- a/testmgmt/generated/MVP2_TestData.xlsx
+++ b/testmgmt/generated/MVP2_TestData.xlsx
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>enh02.reg02.1789505041145@example.test</t>
+          <t>enh02.reg02.1789507809573@example.test</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>enh02.shared.1789505041145@example.test</t>
+          <t>enh02.shared.1789507809573@example.test</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
